--- a/database/event/2135/event_2135_evp_summary.xlsx
+++ b/database/event/2135/event_2135_evp_summary.xlsx
@@ -496,25 +496,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10.8147</v>
+        <v>10.7536</v>
       </c>
       <c r="C2" t="n">
-        <v>8.115500000000001</v>
+        <v>8.069599999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>3.9475</v>
+        <v>3.8403</v>
       </c>
       <c r="E2" t="n">
-        <v>10.8147</v>
+        <v>10.7536</v>
       </c>
       <c r="F2" t="n">
-        <v>4.223</v>
+        <v>4.1619</v>
       </c>
       <c r="G2" t="n">
         <v>6.5917</v>
       </c>
       <c r="H2" t="n">
-        <v>4.3186</v>
+        <v>4.2228</v>
       </c>
       <c r="I2" t="n">
         <v>4.4406</v>
@@ -542,25 +542,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.851699999999999</v>
+        <v>8.765599999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>6.6424</v>
+        <v>6.5778</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1545</v>
+        <v>3.0483</v>
       </c>
       <c r="E3" t="n">
-        <v>8.851699999999999</v>
+        <v>8.765599999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>3.8805</v>
+        <v>3.7944</v>
       </c>
       <c r="G3" t="n">
         <v>4.9712</v>
       </c>
       <c r="H3" t="n">
-        <v>3.8805</v>
+        <v>3.7944</v>
       </c>
       <c r="I3" t="n">
         <v>3.9901</v>
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.613799999999999</v>
+        <v>8.542299999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>6.4639</v>
+        <v>6.4103</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0584</v>
+        <v>2.9593</v>
       </c>
       <c r="E4" t="n">
-        <v>8.613799999999999</v>
+        <v>8.542299999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>4.2392</v>
+        <v>4.1677</v>
       </c>
       <c r="G4" t="n">
         <v>4.3746</v>
       </c>
       <c r="H4" t="n">
-        <v>4.3441</v>
+        <v>4.2319</v>
       </c>
       <c r="I4" t="n">
         <v>4.4876</v>
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.9934</v>
+        <v>7.9502</v>
       </c>
       <c r="C5" t="n">
-        <v>5.9984</v>
+        <v>5.9659</v>
       </c>
       <c r="D5" t="n">
-        <v>2.8078</v>
+        <v>2.7235</v>
       </c>
       <c r="E5" t="n">
-        <v>7.9934</v>
+        <v>7.9502</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9488</v>
+        <v>1.9056</v>
       </c>
       <c r="G5" t="n">
         <v>6.0446</v>
       </c>
       <c r="H5" t="n">
-        <v>1.9488</v>
+        <v>1.9056</v>
       </c>
       <c r="I5" t="n">
         <v>2.0039</v>
@@ -680,25 +680,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.1073</v>
+        <v>6.9976</v>
       </c>
       <c r="C6" t="n">
-        <v>5.3334</v>
+        <v>5.2511</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4498</v>
+        <v>2.3439</v>
       </c>
       <c r="E6" t="n">
-        <v>7.1073</v>
+        <v>6.9976</v>
       </c>
       <c r="F6" t="n">
-        <v>5.7167</v>
+        <v>5.607</v>
       </c>
       <c r="G6" t="n">
         <v>1.3906</v>
       </c>
       <c r="H6" t="n">
-        <v>6.6608</v>
+        <v>6.4888</v>
       </c>
       <c r="I6" t="n">
         <v>6.8808</v>
@@ -726,25 +726,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.9375</v>
+        <v>6.8429</v>
       </c>
       <c r="C7" t="n">
-        <v>5.206</v>
+        <v>5.135</v>
       </c>
       <c r="D7" t="n">
-        <v>2.3812</v>
+        <v>2.2823</v>
       </c>
       <c r="E7" t="n">
-        <v>6.9375</v>
+        <v>6.8429</v>
       </c>
       <c r="F7" t="n">
-        <v>5.734</v>
+        <v>5.6394</v>
       </c>
       <c r="G7" t="n">
         <v>1.2035</v>
       </c>
       <c r="H7" t="n">
-        <v>6.6878</v>
+        <v>6.5395</v>
       </c>
       <c r="I7" t="n">
         <v>6.8767</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.8905</v>
+        <v>6.8073</v>
       </c>
       <c r="C8" t="n">
-        <v>5.1707</v>
+        <v>5.1083</v>
       </c>
       <c r="D8" t="n">
-        <v>2.3622</v>
+        <v>2.2681</v>
       </c>
       <c r="E8" t="n">
-        <v>6.8905</v>
+        <v>6.8073</v>
       </c>
       <c r="F8" t="n">
-        <v>3.7525</v>
+        <v>3.6693</v>
       </c>
       <c r="G8" t="n">
         <v>3.138</v>
       </c>
       <c r="H8" t="n">
-        <v>3.7525</v>
+        <v>3.6693</v>
       </c>
       <c r="I8" t="n">
         <v>3.8585</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.6773</v>
+        <v>6.5869</v>
       </c>
       <c r="C9" t="n">
-        <v>5.0107</v>
+        <v>4.9429</v>
       </c>
       <c r="D9" t="n">
-        <v>2.2761</v>
+        <v>2.1803</v>
       </c>
       <c r="E9" t="n">
-        <v>6.6773</v>
+        <v>6.5869</v>
       </c>
       <c r="F9" t="n">
-        <v>5.5458</v>
+        <v>5.4554</v>
       </c>
       <c r="G9" t="n">
         <v>1.1315</v>
       </c>
       <c r="H9" t="n">
-        <v>6.3928</v>
+        <v>6.251</v>
       </c>
       <c r="I9" t="n">
         <v>6.5734</v>
@@ -864,25 +864,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6.5302</v>
+        <v>6.4331</v>
       </c>
       <c r="C10" t="n">
-        <v>4.9003</v>
+        <v>4.8275</v>
       </c>
       <c r="D10" t="n">
-        <v>2.2167</v>
+        <v>2.119</v>
       </c>
       <c r="E10" t="n">
-        <v>6.5302</v>
+        <v>6.4331</v>
       </c>
       <c r="F10" t="n">
-        <v>5.2298</v>
+        <v>5.1327</v>
       </c>
       <c r="G10" t="n">
         <v>1.3004</v>
       </c>
       <c r="H10" t="n">
-        <v>5.8972</v>
+        <v>5.7449</v>
       </c>
       <c r="I10" t="n">
         <v>6.0921</v>
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6.4043</v>
+        <v>6.3548</v>
       </c>
       <c r="C11" t="n">
-        <v>4.8059</v>
+        <v>4.7687</v>
       </c>
       <c r="D11" t="n">
-        <v>2.1658</v>
+        <v>2.0878</v>
       </c>
       <c r="E11" t="n">
-        <v>6.4043</v>
+        <v>6.3548</v>
       </c>
       <c r="F11" t="n">
-        <v>3.3356</v>
+        <v>3.2861</v>
       </c>
       <c r="G11" t="n">
         <v>3.0687</v>
       </c>
       <c r="H11" t="n">
-        <v>3.3356</v>
+        <v>3.2861</v>
       </c>
       <c r="I11" t="n">
         <v>3.3982</v>
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6.0439</v>
+        <v>5.9328</v>
       </c>
       <c r="C12" t="n">
-        <v>4.5354</v>
+        <v>4.4521</v>
       </c>
       <c r="D12" t="n">
-        <v>2.0202</v>
+        <v>1.9197</v>
       </c>
       <c r="E12" t="n">
-        <v>6.0439</v>
+        <v>5.9328</v>
       </c>
       <c r="F12" t="n">
-        <v>5.7714</v>
+        <v>5.6603</v>
       </c>
       <c r="G12" t="n">
         <v>0.2725</v>
       </c>
       <c r="H12" t="n">
-        <v>6.7464</v>
+        <v>6.5722</v>
       </c>
       <c r="I12" t="n">
         <v>6.9693</v>
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.7762</v>
+        <v>5.6786</v>
       </c>
       <c r="C13" t="n">
-        <v>4.3345</v>
+        <v>4.2613</v>
       </c>
       <c r="D13" t="n">
-        <v>1.9121</v>
+        <v>1.8184</v>
       </c>
       <c r="E13" t="n">
-        <v>5.7762</v>
+        <v>5.6786</v>
       </c>
       <c r="F13" t="n">
-        <v>5.2517</v>
+        <v>5.1541</v>
       </c>
       <c r="G13" t="n">
         <v>0.5245</v>
       </c>
       <c r="H13" t="n">
-        <v>5.9317</v>
+        <v>5.7785</v>
       </c>
       <c r="I13" t="n">
         <v>6.1276</v>
@@ -1048,25 +1048,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.7308</v>
+        <v>5.6519</v>
       </c>
       <c r="C14" t="n">
-        <v>4.3005</v>
+        <v>4.2413</v>
       </c>
       <c r="D14" t="n">
-        <v>1.8938</v>
+        <v>1.8078</v>
       </c>
       <c r="E14" t="n">
-        <v>5.7308</v>
+        <v>5.6519</v>
       </c>
       <c r="F14" t="n">
-        <v>3.5574</v>
+        <v>3.4785</v>
       </c>
       <c r="G14" t="n">
         <v>2.1734</v>
       </c>
       <c r="H14" t="n">
-        <v>3.5574</v>
+        <v>3.4785</v>
       </c>
       <c r="I14" t="n">
         <v>3.6579</v>
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.6181</v>
+        <v>5.5305</v>
       </c>
       <c r="C15" t="n">
-        <v>4.2159</v>
+        <v>4.1502</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8482</v>
+        <v>1.7594</v>
       </c>
       <c r="E15" t="n">
-        <v>5.6181</v>
+        <v>5.5305</v>
       </c>
       <c r="F15" t="n">
-        <v>4.8595</v>
+        <v>4.7719</v>
       </c>
       <c r="G15" t="n">
         <v>0.7586000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>5.3166</v>
+        <v>5.1793</v>
       </c>
       <c r="I15" t="n">
         <v>5.4922</v>
@@ -1136,81 +1136,81 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>fnx</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.5516</v>
+        <v>5.5279</v>
       </c>
       <c r="C16" t="n">
-        <v>4.166</v>
+        <v>4.1482</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8214</v>
+        <v>1.7584</v>
       </c>
       <c r="E16" t="n">
-        <v>5.5516</v>
+        <v>5.5279</v>
       </c>
       <c r="F16" t="n">
-        <v>5.2769</v>
+        <v>4.8663</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2747</v>
+        <v>0.6616</v>
       </c>
       <c r="H16" t="n">
-        <v>5.9711</v>
+        <v>7.8866</v>
       </c>
       <c r="I16" t="n">
-        <v>6.1398</v>
+        <v>6.3923</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2747</v>
+        <v>0.6616</v>
       </c>
       <c r="K16" t="n">
-        <v>203</v>
+        <v>366</v>
       </c>
       <c r="L16" t="n">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="M16" t="n">
-        <v>6.4145</v>
+        <v>7.0539</v>
       </c>
       <c r="N16" t="n">
-        <v>290</v>
+        <v>446</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.5279</v>
+        <v>5.4884</v>
       </c>
       <c r="C17" t="n">
-        <v>4.1482</v>
+        <v>4.1186</v>
       </c>
       <c r="D17" t="n">
-        <v>1.8118</v>
+        <v>1.7427</v>
       </c>
       <c r="E17" t="n">
-        <v>5.5279</v>
+        <v>5.4884</v>
       </c>
       <c r="F17" t="n">
-        <v>4.8663</v>
+        <v>4.6767</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6616</v>
+        <v>0.8117</v>
       </c>
       <c r="H17" t="n">
-        <v>7.8866</v>
+        <v>6.255</v>
       </c>
       <c r="I17" t="n">
-        <v>6.3923</v>
+        <v>5.0699</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6616</v>
+        <v>0.8117</v>
       </c>
       <c r="K17" t="n">
         <v>366</v>
@@ -1219,7 +1219,7 @@
         <v>80</v>
       </c>
       <c r="M17" t="n">
-        <v>7.0539</v>
+        <v>5.8816</v>
       </c>
       <c r="N17" t="n">
         <v>446</v>
@@ -1228,47 +1228,47 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>fnx</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.4884</v>
+        <v>5.4672</v>
       </c>
       <c r="C18" t="n">
-        <v>4.1186</v>
+        <v>4.1027</v>
       </c>
       <c r="D18" t="n">
-        <v>1.7958</v>
+        <v>1.7342</v>
       </c>
       <c r="E18" t="n">
-        <v>5.4884</v>
+        <v>5.4672</v>
       </c>
       <c r="F18" t="n">
-        <v>4.6767</v>
+        <v>5.1925</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8117</v>
+        <v>0.2747</v>
       </c>
       <c r="H18" t="n">
-        <v>6.255</v>
+        <v>5.8387</v>
       </c>
       <c r="I18" t="n">
-        <v>5.0699</v>
+        <v>6.1398</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8117</v>
+        <v>0.2747</v>
       </c>
       <c r="K18" t="n">
-        <v>366</v>
+        <v>203</v>
       </c>
       <c r="L18" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="M18" t="n">
-        <v>5.8816</v>
+        <v>6.4145</v>
       </c>
       <c r="N18" t="n">
-        <v>446</v>
+        <v>290</v>
       </c>
     </row>
     <row r="19">
@@ -1278,25 +1278,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.2533</v>
+        <v>5.2111</v>
       </c>
       <c r="C19" t="n">
-        <v>3.9421</v>
+        <v>3.9105</v>
       </c>
       <c r="D19" t="n">
-        <v>1.7009</v>
+        <v>1.6322</v>
       </c>
       <c r="E19" t="n">
-        <v>5.2533</v>
+        <v>5.2111</v>
       </c>
       <c r="F19" t="n">
-        <v>5.2533</v>
+        <v>5.2111</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>5.9342</v>
+        <v>5.868</v>
       </c>
       <c r="I19" t="n">
         <v>6.0174</v>
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.0969</v>
+        <v>5.0277</v>
       </c>
       <c r="C20" t="n">
-        <v>3.8248</v>
+        <v>3.7729</v>
       </c>
       <c r="D20" t="n">
-        <v>1.6377</v>
+        <v>1.5591</v>
       </c>
       <c r="E20" t="n">
-        <v>5.0969</v>
+        <v>5.0277</v>
       </c>
       <c r="F20" t="n">
-        <v>3.1203</v>
+        <v>3.0511</v>
       </c>
       <c r="G20" t="n">
         <v>1.9766</v>
       </c>
       <c r="H20" t="n">
-        <v>3.1203</v>
+        <v>3.0511</v>
       </c>
       <c r="I20" t="n">
         <v>3.2085</v>
@@ -1370,25 +1370,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5.0539</v>
+        <v>5.0155</v>
       </c>
       <c r="C21" t="n">
-        <v>3.7925</v>
+        <v>3.7637</v>
       </c>
       <c r="D21" t="n">
-        <v>1.6203</v>
+        <v>1.5543</v>
       </c>
       <c r="E21" t="n">
-        <v>5.0539</v>
+        <v>5.0155</v>
       </c>
       <c r="F21" t="n">
-        <v>3.4472</v>
+        <v>3.4088</v>
       </c>
       <c r="G21" t="n">
         <v>1.6067</v>
       </c>
       <c r="H21" t="n">
-        <v>3.4472</v>
+        <v>3.4088</v>
       </c>
       <c r="I21" t="n">
         <v>3.4956</v>
@@ -1416,25 +1416,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4.9247</v>
+        <v>4.8354</v>
       </c>
       <c r="C22" t="n">
-        <v>3.6956</v>
+        <v>3.6285</v>
       </c>
       <c r="D22" t="n">
-        <v>1.5681</v>
+        <v>1.4825</v>
       </c>
       <c r="E22" t="n">
-        <v>4.9247</v>
+        <v>4.8354</v>
       </c>
       <c r="F22" t="n">
-        <v>4.9247</v>
+        <v>4.8354</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>5.4188</v>
+        <v>5.2789</v>
       </c>
       <c r="I22" t="n">
         <v>5.5978</v>
@@ -1462,25 +1462,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4.8303</v>
+        <v>4.7403</v>
       </c>
       <c r="C23" t="n">
-        <v>3.6247</v>
+        <v>3.5572</v>
       </c>
       <c r="D23" t="n">
-        <v>1.53</v>
+        <v>1.4446</v>
       </c>
       <c r="E23" t="n">
-        <v>4.8303</v>
+        <v>4.7403</v>
       </c>
       <c r="F23" t="n">
-        <v>5.5269</v>
+        <v>5.4369</v>
       </c>
       <c r="G23" t="n">
         <v>-0.6966</v>
       </c>
       <c r="H23" t="n">
-        <v>6.363</v>
+        <v>6.2219</v>
       </c>
       <c r="I23" t="n">
         <v>6.5428</v>
@@ -1508,25 +1508,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4.6745</v>
+        <v>4.6003</v>
       </c>
       <c r="C24" t="n">
-        <v>3.5078</v>
+        <v>3.4521</v>
       </c>
       <c r="D24" t="n">
-        <v>1.467</v>
+        <v>1.3888</v>
       </c>
       <c r="E24" t="n">
-        <v>4.6745</v>
+        <v>4.6003</v>
       </c>
       <c r="F24" t="n">
-        <v>4.3425</v>
+        <v>4.2683</v>
       </c>
       <c r="G24" t="n">
         <v>0.332</v>
       </c>
       <c r="H24" t="n">
-        <v>4.5061</v>
+        <v>4.3897</v>
       </c>
       <c r="I24" t="n">
         <v>4.6549</v>
@@ -1554,25 +1554,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.5681</v>
+        <v>4.5034</v>
       </c>
       <c r="C25" t="n">
-        <v>3.428</v>
+        <v>3.3794</v>
       </c>
       <c r="D25" t="n">
-        <v>1.424</v>
+        <v>1.3502</v>
       </c>
       <c r="E25" t="n">
-        <v>4.5681</v>
+        <v>4.5034</v>
       </c>
       <c r="F25" t="n">
-        <v>4.3866</v>
+        <v>4.3219</v>
       </c>
       <c r="G25" t="n">
         <v>0.1815</v>
       </c>
       <c r="H25" t="n">
-        <v>4.5752</v>
+        <v>4.4737</v>
       </c>
       <c r="I25" t="n">
         <v>4.7044</v>
@@ -1596,93 +1596,93 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ScreaM</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.5618</v>
+        <v>4.4849</v>
       </c>
       <c r="C26" t="n">
-        <v>3.4232</v>
+        <v>3.3655</v>
       </c>
       <c r="D26" t="n">
-        <v>1.4215</v>
+        <v>1.3429</v>
       </c>
       <c r="E26" t="n">
-        <v>4.5618</v>
+        <v>4.4849</v>
       </c>
       <c r="F26" t="n">
-        <v>4.5618</v>
+        <v>4.784</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>-0.2991</v>
       </c>
       <c r="H26" t="n">
-        <v>4.8498</v>
+        <v>5.1983</v>
       </c>
       <c r="I26" t="n">
-        <v>5.01</v>
+        <v>5.4663</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>-0.2991</v>
       </c>
       <c r="K26" t="n">
-        <v>353</v>
+        <v>231</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="M26" t="n">
-        <v>5.01</v>
+        <v>5.1672</v>
       </c>
       <c r="N26" t="n">
-        <v>353</v>
+        <v>370</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>seized</t>
+          <t>ScreaM</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4.5601</v>
+        <v>4.4819</v>
       </c>
       <c r="C27" t="n">
-        <v>3.422</v>
+        <v>3.3633</v>
       </c>
       <c r="D27" t="n">
-        <v>1.4208</v>
+        <v>1.3417</v>
       </c>
       <c r="E27" t="n">
-        <v>4.5601</v>
+        <v>4.4819</v>
       </c>
       <c r="F27" t="n">
-        <v>4.8592</v>
+        <v>4.4819</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.2991</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>5.3161</v>
+        <v>4.7246</v>
       </c>
       <c r="I27" t="n">
-        <v>5.4663</v>
+        <v>5.01</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.2991</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>231</v>
+        <v>353</v>
       </c>
       <c r="L27" t="n">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>5.1672</v>
+        <v>5.01</v>
       </c>
       <c r="N27" t="n">
-        <v>370</v>
+        <v>353</v>
       </c>
     </row>
     <row r="28">
@@ -1692,25 +1692,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4.4853</v>
+        <v>4.4449</v>
       </c>
       <c r="C28" t="n">
-        <v>3.3658</v>
+        <v>3.3355</v>
       </c>
       <c r="D28" t="n">
-        <v>1.3906</v>
+        <v>1.3269</v>
       </c>
       <c r="E28" t="n">
-        <v>4.4853</v>
+        <v>4.4449</v>
       </c>
       <c r="F28" t="n">
-        <v>3.6239</v>
+        <v>3.5835</v>
       </c>
       <c r="G28" t="n">
         <v>0.8614000000000001</v>
       </c>
       <c r="H28" t="n">
-        <v>3.6239</v>
+        <v>3.5835</v>
       </c>
       <c r="I28" t="n">
         <v>3.6748</v>
@@ -1738,25 +1738,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4.4343</v>
+        <v>4.3615</v>
       </c>
       <c r="C29" t="n">
-        <v>3.3276</v>
+        <v>3.2729</v>
       </c>
       <c r="D29" t="n">
-        <v>1.37</v>
+        <v>1.2937</v>
       </c>
       <c r="E29" t="n">
-        <v>4.4343</v>
+        <v>4.3615</v>
       </c>
       <c r="F29" t="n">
-        <v>4.7493</v>
+        <v>4.6765</v>
       </c>
       <c r="G29" t="n">
         <v>-0.315</v>
       </c>
       <c r="H29" t="n">
-        <v>5.1438</v>
+        <v>5.0297</v>
       </c>
       <c r="I29" t="n">
         <v>5.2891</v>
@@ -1790,7 +1790,7 @@
         <v>3.2559</v>
       </c>
       <c r="D30" t="n">
-        <v>1.3314</v>
+        <v>1.2847</v>
       </c>
       <c r="E30" t="n">
         <v>4.3388</v>
@@ -1830,25 +1830,25 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4.2568</v>
+        <v>4.195</v>
       </c>
       <c r="C31" t="n">
-        <v>3.1944</v>
+        <v>3.148</v>
       </c>
       <c r="D31" t="n">
-        <v>1.2983</v>
+        <v>1.2274</v>
       </c>
       <c r="E31" t="n">
-        <v>4.2568</v>
+        <v>4.195</v>
       </c>
       <c r="F31" t="n">
-        <v>4.2568</v>
+        <v>4.195</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>4.3716</v>
+        <v>4.2747</v>
       </c>
       <c r="I31" t="n">
         <v>4.4951</v>
@@ -1876,25 +1876,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4.2119</v>
+        <v>4.1119</v>
       </c>
       <c r="C32" t="n">
-        <v>3.1607</v>
+        <v>3.0856</v>
       </c>
       <c r="D32" t="n">
-        <v>1.2802</v>
+        <v>1.1943</v>
       </c>
       <c r="E32" t="n">
-        <v>4.2119</v>
+        <v>4.1119</v>
       </c>
       <c r="F32" t="n">
-        <v>3.8695</v>
+        <v>3.7695</v>
       </c>
       <c r="G32" t="n">
         <v>0.3424</v>
       </c>
       <c r="H32" t="n">
-        <v>3.8695</v>
+        <v>3.7695</v>
       </c>
       <c r="I32" t="n">
         <v>3.9973</v>
@@ -1922,25 +1922,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3.9807</v>
+        <v>3.941</v>
       </c>
       <c r="C33" t="n">
-        <v>2.9872</v>
+        <v>2.9574</v>
       </c>
       <c r="D33" t="n">
-        <v>1.1868</v>
+        <v>1.1262</v>
       </c>
       <c r="E33" t="n">
-        <v>3.9807</v>
+        <v>3.941</v>
       </c>
       <c r="F33" t="n">
-        <v>2.6754</v>
+        <v>2.6357</v>
       </c>
       <c r="G33" t="n">
         <v>1.3053</v>
       </c>
       <c r="H33" t="n">
-        <v>2.6754</v>
+        <v>2.6357</v>
       </c>
       <c r="I33" t="n">
         <v>2.7256</v>
@@ -1968,25 +1968,25 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3.8471</v>
+        <v>3.7852</v>
       </c>
       <c r="C34" t="n">
-        <v>2.8869</v>
+        <v>2.8405</v>
       </c>
       <c r="D34" t="n">
-        <v>1.1328</v>
+        <v>1.0641</v>
       </c>
       <c r="E34" t="n">
-        <v>3.8471</v>
+        <v>3.7852</v>
       </c>
       <c r="F34" t="n">
-        <v>4.2603</v>
+        <v>4.1984</v>
       </c>
       <c r="G34" t="n">
         <v>-0.4132</v>
       </c>
       <c r="H34" t="n">
-        <v>4.3771</v>
+        <v>4.2801</v>
       </c>
       <c r="I34" t="n">
         <v>4.5008</v>
@@ -2014,25 +2014,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3.7588</v>
+        <v>3.6611</v>
       </c>
       <c r="C35" t="n">
-        <v>2.8207</v>
+        <v>2.7473</v>
       </c>
       <c r="D35" t="n">
-        <v>1.0971</v>
+        <v>1.0147</v>
       </c>
       <c r="E35" t="n">
-        <v>3.7588</v>
+        <v>3.6611</v>
       </c>
       <c r="F35" t="n">
-        <v>3.7827</v>
+        <v>3.685</v>
       </c>
       <c r="G35" t="n">
         <v>-0.0239</v>
       </c>
       <c r="H35" t="n">
-        <v>3.7827</v>
+        <v>3.685</v>
       </c>
       <c r="I35" t="n">
         <v>3.9077</v>
@@ -2060,25 +2060,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3.7375</v>
+        <v>3.66</v>
       </c>
       <c r="C36" t="n">
-        <v>2.8047</v>
+        <v>2.7465</v>
       </c>
       <c r="D36" t="n">
-        <v>1.0885</v>
+        <v>1.0142</v>
       </c>
       <c r="E36" t="n">
-        <v>3.7375</v>
+        <v>3.66</v>
       </c>
       <c r="F36" t="n">
-        <v>3.4943</v>
+        <v>3.4168</v>
       </c>
       <c r="G36" t="n">
         <v>0.2432</v>
       </c>
       <c r="H36" t="n">
-        <v>3.4943</v>
+        <v>3.4168</v>
       </c>
       <c r="I36" t="n">
         <v>3.593</v>
@@ -2106,25 +2106,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3.6694</v>
+        <v>3.6285</v>
       </c>
       <c r="C37" t="n">
-        <v>2.7536</v>
+        <v>2.7229</v>
       </c>
       <c r="D37" t="n">
-        <v>1.061</v>
+        <v>1.0017</v>
       </c>
       <c r="E37" t="n">
-        <v>3.6694</v>
+        <v>3.6285</v>
       </c>
       <c r="F37" t="n">
-        <v>3.6694</v>
+        <v>3.6285</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>3.6694</v>
+        <v>3.6285</v>
       </c>
       <c r="I37" t="n">
         <v>3.7208</v>
@@ -2152,25 +2152,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3.6049</v>
+        <v>3.5718</v>
       </c>
       <c r="C38" t="n">
-        <v>2.7052</v>
+        <v>2.6803</v>
       </c>
       <c r="D38" t="n">
-        <v>1.0349</v>
+        <v>0.9791</v>
       </c>
       <c r="E38" t="n">
-        <v>3.6049</v>
+        <v>3.5718</v>
       </c>
       <c r="F38" t="n">
-        <v>2.9652</v>
+        <v>2.9321</v>
       </c>
       <c r="G38" t="n">
         <v>0.6397</v>
       </c>
       <c r="H38" t="n">
-        <v>2.9652</v>
+        <v>2.9321</v>
       </c>
       <c r="I38" t="n">
         <v>3.0068</v>
@@ -2198,25 +2198,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3.5573</v>
+        <v>3.4919</v>
       </c>
       <c r="C39" t="n">
-        <v>2.6694</v>
+        <v>2.6204</v>
       </c>
       <c r="D39" t="n">
-        <v>1.0157</v>
+        <v>0.9473</v>
       </c>
       <c r="E39" t="n">
-        <v>3.5573</v>
+        <v>3.4919</v>
       </c>
       <c r="F39" t="n">
-        <v>4.4182</v>
+        <v>4.3528</v>
       </c>
       <c r="G39" t="n">
         <v>-0.8609</v>
       </c>
       <c r="H39" t="n">
-        <v>4.6247</v>
+        <v>4.5222</v>
       </c>
       <c r="I39" t="n">
         <v>4.7554</v>
@@ -2244,25 +2244,25 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3.3629</v>
+        <v>3.2659</v>
       </c>
       <c r="C40" t="n">
-        <v>2.5236</v>
+        <v>2.4508</v>
       </c>
       <c r="D40" t="n">
-        <v>0.9372</v>
+        <v>0.8572</v>
       </c>
       <c r="E40" t="n">
-        <v>3.3629</v>
+        <v>3.2659</v>
       </c>
       <c r="F40" t="n">
-        <v>3.7563</v>
+        <v>3.6593</v>
       </c>
       <c r="G40" t="n">
         <v>-0.3934</v>
       </c>
       <c r="H40" t="n">
-        <v>3.7563</v>
+        <v>3.6593</v>
       </c>
       <c r="I40" t="n">
         <v>3.8804</v>
@@ -2290,25 +2290,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2.7306</v>
+        <v>2.6724</v>
       </c>
       <c r="C41" t="n">
-        <v>2.0491</v>
+        <v>2.0054</v>
       </c>
       <c r="D41" t="n">
-        <v>0.6817</v>
+        <v>0.6208</v>
       </c>
       <c r="E41" t="n">
-        <v>2.7306</v>
+        <v>2.6724</v>
       </c>
       <c r="F41" t="n">
-        <v>2.6256</v>
+        <v>2.5674</v>
       </c>
       <c r="G41" t="n">
         <v>0.105</v>
       </c>
       <c r="H41" t="n">
-        <v>2.6256</v>
+        <v>2.5674</v>
       </c>
       <c r="I41" t="n">
         <v>2.6998</v>
@@ -2336,25 +2336,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2.5728</v>
+        <v>2.5536</v>
       </c>
       <c r="C42" t="n">
-        <v>1.9307</v>
+        <v>1.9163</v>
       </c>
       <c r="D42" t="n">
-        <v>0.618</v>
+        <v>0.5734</v>
       </c>
       <c r="E42" t="n">
-        <v>2.5728</v>
+        <v>2.5536</v>
       </c>
       <c r="F42" t="n">
-        <v>2.5728</v>
+        <v>2.5536</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>2.5728</v>
+        <v>2.5536</v>
       </c>
       <c r="I42" t="n">
         <v>2.5968</v>
@@ -2388,7 +2388,7 @@
         <v>1.8501</v>
       </c>
       <c r="D43" t="n">
-        <v>0.5746</v>
+        <v>0.5383</v>
       </c>
       <c r="E43" t="n">
         <v>2.4655</v>
@@ -2434,7 +2434,7 @@
         <v>1.7406</v>
       </c>
       <c r="D44" t="n">
-        <v>0.5157</v>
+        <v>0.4802</v>
       </c>
       <c r="E44" t="n">
         <v>2.3195</v>
@@ -2474,25 +2474,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2.2917</v>
+        <v>2.2661</v>
       </c>
       <c r="C45" t="n">
-        <v>1.7197</v>
+        <v>1.7005</v>
       </c>
       <c r="D45" t="n">
-        <v>0.5044</v>
+        <v>0.4589</v>
       </c>
       <c r="E45" t="n">
-        <v>2.2917</v>
+        <v>2.2661</v>
       </c>
       <c r="F45" t="n">
-        <v>2.2917</v>
+        <v>2.2661</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>2.2917</v>
+        <v>2.2661</v>
       </c>
       <c r="I45" t="n">
         <v>2.3238</v>
@@ -2520,25 +2520,25 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2.2697</v>
+        <v>2.2645</v>
       </c>
       <c r="C46" t="n">
-        <v>1.7032</v>
+        <v>1.6993</v>
       </c>
       <c r="D46" t="n">
-        <v>0.4955</v>
+        <v>0.4583</v>
       </c>
       <c r="E46" t="n">
-        <v>2.2697</v>
+        <v>2.2645</v>
       </c>
       <c r="F46" t="n">
-        <v>0.357</v>
+        <v>0.3518</v>
       </c>
       <c r="G46" t="n">
         <v>1.9127</v>
       </c>
       <c r="H46" t="n">
-        <v>0.357</v>
+        <v>0.3518</v>
       </c>
       <c r="I46" t="n">
         <v>0.3637</v>
@@ -2572,7 +2572,7 @@
         <v>1.672</v>
       </c>
       <c r="D47" t="n">
-        <v>0.4787</v>
+        <v>0.4438</v>
       </c>
       <c r="E47" t="n">
         <v>2.2281</v>
@@ -2612,25 +2612,25 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2.1182</v>
+        <v>2.1103</v>
       </c>
       <c r="C48" t="n">
-        <v>1.5895</v>
+        <v>1.5836</v>
       </c>
       <c r="D48" t="n">
-        <v>0.4343</v>
+        <v>0.3968</v>
       </c>
       <c r="E48" t="n">
-        <v>2.1182</v>
+        <v>2.1103</v>
       </c>
       <c r="F48" t="n">
-        <v>2.1182</v>
+        <v>2.1103</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>2.1182</v>
+        <v>2.1103</v>
       </c>
       <c r="I48" t="n">
         <v>2.128</v>
@@ -2664,7 +2664,7 @@
         <v>1.4075</v>
       </c>
       <c r="D49" t="n">
-        <v>0.3363</v>
+        <v>0.3033</v>
       </c>
       <c r="E49" t="n">
         <v>1.8756</v>
@@ -2704,25 +2704,25 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1.7619</v>
+        <v>1.7164</v>
       </c>
       <c r="C50" t="n">
-        <v>1.3222</v>
+        <v>1.288</v>
       </c>
       <c r="D50" t="n">
-        <v>0.2904</v>
+        <v>0.2399</v>
       </c>
       <c r="E50" t="n">
-        <v>1.7619</v>
+        <v>1.7164</v>
       </c>
       <c r="F50" t="n">
-        <v>1.7619</v>
+        <v>1.7164</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>1.7619</v>
+        <v>1.7164</v>
       </c>
       <c r="I50" t="n">
         <v>1.8201</v>
@@ -2756,7 +2756,7 @@
         <v>1.2552</v>
       </c>
       <c r="D51" t="n">
-        <v>0.2544</v>
+        <v>0.2225</v>
       </c>
       <c r="E51" t="n">
         <v>1.6727</v>
@@ -2796,25 +2796,25 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1.6126</v>
+        <v>1.582</v>
       </c>
       <c r="C52" t="n">
-        <v>1.2101</v>
+        <v>1.1872</v>
       </c>
       <c r="D52" t="n">
-        <v>0.2301</v>
+        <v>0.1864</v>
       </c>
       <c r="E52" t="n">
-        <v>1.6126</v>
+        <v>1.582</v>
       </c>
       <c r="F52" t="n">
-        <v>1.1837</v>
+        <v>1.1531</v>
       </c>
       <c r="G52" t="n">
         <v>0.4289</v>
       </c>
       <c r="H52" t="n">
-        <v>1.1837</v>
+        <v>1.1531</v>
       </c>
       <c r="I52" t="n">
         <v>1.2228</v>
@@ -2842,25 +2842,25 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1.5173</v>
+        <v>1.4601</v>
       </c>
       <c r="C53" t="n">
-        <v>1.1386</v>
+        <v>1.0957</v>
       </c>
       <c r="D53" t="n">
-        <v>0.1916</v>
+        <v>0.1378</v>
       </c>
       <c r="E53" t="n">
-        <v>1.5173</v>
+        <v>1.4601</v>
       </c>
       <c r="F53" t="n">
-        <v>2.2151</v>
+        <v>2.1579</v>
       </c>
       <c r="G53" t="n">
         <v>-0.6978</v>
       </c>
       <c r="H53" t="n">
-        <v>2.2151</v>
+        <v>2.1579</v>
       </c>
       <c r="I53" t="n">
         <v>2.2883</v>
@@ -2894,7 +2894,7 @@
         <v>1.0945</v>
       </c>
       <c r="D54" t="n">
-        <v>0.1678</v>
+        <v>0.1372</v>
       </c>
       <c r="E54" t="n">
         <v>1.4585</v>
@@ -2934,25 +2934,25 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1.3501</v>
+        <v>1.335</v>
       </c>
       <c r="C55" t="n">
-        <v>1.0131</v>
+        <v>1.0018</v>
       </c>
       <c r="D55" t="n">
-        <v>0.124</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="E55" t="n">
-        <v>1.3501</v>
+        <v>1.335</v>
       </c>
       <c r="F55" t="n">
-        <v>1.3501</v>
+        <v>1.335</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>1.3501</v>
+        <v>1.335</v>
       </c>
       <c r="I55" t="n">
         <v>1.369</v>
@@ -2986,7 +2986,7 @@
         <v>0.9865</v>
       </c>
       <c r="D56" t="n">
-        <v>0.1097</v>
+        <v>0.0798</v>
       </c>
       <c r="E56" t="n">
         <v>1.3146</v>
@@ -3022,93 +3022,93 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>fox</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1.2659</v>
+        <v>1.2305</v>
       </c>
       <c r="C57" t="n">
-        <v>0.9499</v>
+        <v>0.9234</v>
       </c>
       <c r="D57" t="n">
-        <v>0.09</v>
+        <v>0.0463</v>
       </c>
       <c r="E57" t="n">
-        <v>1.2659</v>
+        <v>1.2305</v>
       </c>
       <c r="F57" t="n">
-        <v>2.2659</v>
+        <v>1.7744</v>
       </c>
       <c r="G57" t="n">
-        <v>-1</v>
+        <v>-0.5439000000000001</v>
       </c>
       <c r="H57" t="n">
-        <v>2.2659</v>
+        <v>1.7744</v>
       </c>
       <c r="I57" t="n">
-        <v>2.3408</v>
+        <v>1.4382</v>
       </c>
       <c r="J57" t="n">
-        <v>-1</v>
+        <v>-0.5439000000000001</v>
       </c>
       <c r="K57" t="n">
-        <v>269</v>
+        <v>366</v>
       </c>
       <c r="L57" t="n">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="M57" t="n">
-        <v>1.3408</v>
+        <v>0.8942999999999999</v>
       </c>
       <c r="N57" t="n">
-        <v>321</v>
+        <v>446</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>fox</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1.2305</v>
+        <v>1.2074</v>
       </c>
       <c r="C58" t="n">
-        <v>0.9234</v>
+        <v>0.906</v>
       </c>
       <c r="D58" t="n">
-        <v>0.0757</v>
+        <v>0.0371</v>
       </c>
       <c r="E58" t="n">
-        <v>1.2305</v>
+        <v>1.2074</v>
       </c>
       <c r="F58" t="n">
-        <v>1.7744</v>
+        <v>2.2074</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.5439000000000001</v>
+        <v>-1</v>
       </c>
       <c r="H58" t="n">
-        <v>1.7744</v>
+        <v>2.2074</v>
       </c>
       <c r="I58" t="n">
-        <v>1.4382</v>
+        <v>2.3408</v>
       </c>
       <c r="J58" t="n">
-        <v>-0.5439000000000001</v>
+        <v>-1</v>
       </c>
       <c r="K58" t="n">
-        <v>366</v>
+        <v>269</v>
       </c>
       <c r="L58" t="n">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="M58" t="n">
-        <v>0.8942999999999999</v>
+        <v>1.3408</v>
       </c>
       <c r="N58" t="n">
-        <v>446</v>
+        <v>321</v>
       </c>
     </row>
     <row r="59">
@@ -3118,25 +3118,25 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1.1692</v>
+        <v>1.139</v>
       </c>
       <c r="C59" t="n">
-        <v>0.8774</v>
+        <v>0.8547</v>
       </c>
       <c r="D59" t="n">
-        <v>0.051</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="E59" t="n">
-        <v>1.1692</v>
+        <v>1.139</v>
       </c>
       <c r="F59" t="n">
-        <v>1.1692</v>
+        <v>1.139</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>1.1692</v>
+        <v>1.139</v>
       </c>
       <c r="I59" t="n">
         <v>1.2078</v>
@@ -3170,7 +3170,7 @@
         <v>0.8538</v>
       </c>
       <c r="D60" t="n">
-        <v>0.0383</v>
+        <v>0.0094</v>
       </c>
       <c r="E60" t="n">
         <v>1.1378</v>
@@ -3210,25 +3210,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1.125</v>
+        <v>1.1125</v>
       </c>
       <c r="C61" t="n">
-        <v>0.8442</v>
+        <v>0.8348</v>
       </c>
       <c r="D61" t="n">
-        <v>0.0331</v>
+        <v>-0.0007</v>
       </c>
       <c r="E61" t="n">
-        <v>1.125</v>
+        <v>1.1125</v>
       </c>
       <c r="F61" t="n">
-        <v>1.125</v>
+        <v>1.1125</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>1.125</v>
+        <v>1.1125</v>
       </c>
       <c r="I61" t="n">
         <v>1.1408</v>
@@ -3256,25 +3256,25 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1.0929</v>
+        <v>1.0847</v>
       </c>
       <c r="C62" t="n">
-        <v>0.8201000000000001</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="D62" t="n">
-        <v>0.0201</v>
+        <v>-0.0118</v>
       </c>
       <c r="E62" t="n">
-        <v>1.0929</v>
+        <v>1.0847</v>
       </c>
       <c r="F62" t="n">
-        <v>1.0929</v>
+        <v>1.0847</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>1.0929</v>
+        <v>1.0847</v>
       </c>
       <c r="I62" t="n">
         <v>1.1031</v>
@@ -3302,25 +3302,25 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1.0729</v>
+        <v>1.0685</v>
       </c>
       <c r="C63" t="n">
-        <v>0.8051</v>
+        <v>0.8018</v>
       </c>
       <c r="D63" t="n">
-        <v>0.0121</v>
+        <v>-0.0182</v>
       </c>
       <c r="E63" t="n">
-        <v>1.0729</v>
+        <v>1.0685</v>
       </c>
       <c r="F63" t="n">
-        <v>0.3986</v>
+        <v>0.3942</v>
       </c>
       <c r="G63" t="n">
         <v>0.6743</v>
       </c>
       <c r="H63" t="n">
-        <v>0.3986</v>
+        <v>0.3942</v>
       </c>
       <c r="I63" t="n">
         <v>0.4042</v>
@@ -3354,7 +3354,7 @@
         <v>0.7488</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.0183</v>
+        <v>-0.0464</v>
       </c>
       <c r="E64" t="n">
         <v>0.9978</v>
@@ -3394,25 +3394,25 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.9026999999999999</v>
+        <v>0.8544</v>
       </c>
       <c r="C65" t="n">
-        <v>0.6774</v>
+        <v>0.6412</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.0567</v>
+        <v>-0.1035</v>
       </c>
       <c r="E65" t="n">
-        <v>0.9026999999999999</v>
+        <v>0.8544</v>
       </c>
       <c r="F65" t="n">
-        <v>1.8716</v>
+        <v>1.8233</v>
       </c>
       <c r="G65" t="n">
         <v>-0.9689</v>
       </c>
       <c r="H65" t="n">
-        <v>1.8716</v>
+        <v>1.8233</v>
       </c>
       <c r="I65" t="n">
         <v>1.9335</v>
@@ -3440,25 +3440,25 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.8752</v>
+        <v>0.8336</v>
       </c>
       <c r="C66" t="n">
-        <v>0.6568000000000001</v>
+        <v>0.6254999999999999</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.0678</v>
+        <v>-0.1118</v>
       </c>
       <c r="E66" t="n">
-        <v>0.8752</v>
+        <v>0.8336</v>
       </c>
       <c r="F66" t="n">
-        <v>1.8752</v>
+        <v>1.8336</v>
       </c>
       <c r="G66" t="n">
         <v>-1</v>
       </c>
       <c r="H66" t="n">
-        <v>1.8752</v>
+        <v>1.8336</v>
       </c>
       <c r="I66" t="n">
         <v>1.9281</v>
@@ -3486,25 +3486,25 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.6921</v>
+        <v>0.6895</v>
       </c>
       <c r="C67" t="n">
-        <v>0.5194</v>
+        <v>0.5174</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.1418</v>
+        <v>-0.1692</v>
       </c>
       <c r="E67" t="n">
-        <v>0.6921</v>
+        <v>0.6895</v>
       </c>
       <c r="F67" t="n">
-        <v>0.6921</v>
+        <v>0.6895</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>0.6921</v>
+        <v>0.6895</v>
       </c>
       <c r="I67" t="n">
         <v>0.6953</v>
@@ -3532,25 +3532,25 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.6568000000000001</v>
+        <v>0.6544</v>
       </c>
       <c r="C68" t="n">
-        <v>0.4929</v>
+        <v>0.4911</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.156</v>
+        <v>-0.1832</v>
       </c>
       <c r="E68" t="n">
-        <v>0.6568000000000001</v>
+        <v>0.6544</v>
       </c>
       <c r="F68" t="n">
-        <v>0.6568000000000001</v>
+        <v>0.6544</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>0.6568000000000001</v>
+        <v>0.6544</v>
       </c>
       <c r="I68" t="n">
         <v>0.6599</v>
@@ -3578,25 +3578,25 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.6558</v>
+        <v>0.6534</v>
       </c>
       <c r="C69" t="n">
-        <v>0.4921</v>
+        <v>0.4903</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.1564</v>
+        <v>-0.1836</v>
       </c>
       <c r="E69" t="n">
-        <v>0.6558</v>
+        <v>0.6534</v>
       </c>
       <c r="F69" t="n">
-        <v>0.6558</v>
+        <v>0.6534</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>0.6558</v>
+        <v>0.6534</v>
       </c>
       <c r="I69" t="n">
         <v>0.6589</v>
@@ -3630,7 +3630,7 @@
         <v>0.4506</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.1788</v>
+        <v>-0.2047</v>
       </c>
       <c r="E70" t="n">
         <v>0.6005</v>
@@ -3670,25 +3670,25 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.4925</v>
+        <v>0.4907</v>
       </c>
       <c r="C71" t="n">
-        <v>0.3696</v>
+        <v>0.3682</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.2224</v>
+        <v>-0.2484</v>
       </c>
       <c r="E71" t="n">
-        <v>0.4925</v>
+        <v>0.4907</v>
       </c>
       <c r="F71" t="n">
-        <v>0.4925</v>
+        <v>0.4907</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>0.4925</v>
+        <v>0.4907</v>
       </c>
       <c r="I71" t="n">
         <v>0.4948</v>
@@ -3716,25 +3716,25 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.1782</v>
+        <v>0.1769</v>
       </c>
       <c r="C72" t="n">
-        <v>0.1337</v>
+        <v>0.1327</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.3494</v>
+        <v>-0.3734</v>
       </c>
       <c r="E72" t="n">
-        <v>0.1782</v>
+        <v>0.1769</v>
       </c>
       <c r="F72" t="n">
-        <v>0.1782</v>
+        <v>0.1769</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>0.1782</v>
+        <v>0.1769</v>
       </c>
       <c r="I72" t="n">
         <v>0.1799</v>
@@ -3768,7 +3768,7 @@
         <v>0.06619999999999999</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.3857</v>
+        <v>-0.4088</v>
       </c>
       <c r="E73" t="n">
         <v>0.0882</v>
@@ -3808,25 +3808,25 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.0694</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="C74" t="n">
-        <v>0.0521</v>
+        <v>0.0519</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.3933</v>
+        <v>-0.4164</v>
       </c>
       <c r="E74" t="n">
-        <v>0.0694</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="F74" t="n">
-        <v>0.0694</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>0.0694</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="I74" t="n">
         <v>0.0697</v>
@@ -3860,7 +3860,7 @@
         <v>0.0396</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.4</v>
+        <v>-0.4229</v>
       </c>
       <c r="E75" t="n">
         <v>0.0528</v>
@@ -3900,25 +3900,25 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-0.1773</v>
+        <v>-0.16</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.133</v>
+        <v>-0.1201</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.493</v>
+        <v>-0.5077</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.1773</v>
+        <v>-0.16</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.1678</v>
+        <v>-1.1505</v>
       </c>
       <c r="G76" t="n">
         <v>0.9905</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.1678</v>
+        <v>-1.1505</v>
       </c>
       <c r="I76" t="n">
         <v>-1.1897</v>
@@ -3942,93 +3942,93 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Surreal</t>
+          <t>denis</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-0.4194</v>
+        <v>-0.4172</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.3147</v>
+        <v>-0.3131</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.5908</v>
+        <v>-0.6101</v>
       </c>
       <c r="E77" t="n">
-        <v>-0.4194</v>
+        <v>-0.4172</v>
       </c>
       <c r="F77" t="n">
-        <v>-0.4194</v>
+        <v>-1.3934</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>0.9762</v>
       </c>
       <c r="H77" t="n">
-        <v>-0.4194</v>
+        <v>-1.3934</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.4194</v>
+        <v>-1.4409</v>
       </c>
       <c r="J77" t="n">
-        <v>0</v>
+        <v>0.9762</v>
       </c>
       <c r="K77" t="n">
-        <v>211</v>
+        <v>316</v>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="M77" t="n">
-        <v>-0.4194</v>
+        <v>-0.4647000000000001</v>
       </c>
       <c r="N77" t="n">
-        <v>211</v>
+        <v>491</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>denis</t>
+          <t>Surreal</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-0.4382</v>
+        <v>-0.4194</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.3288</v>
+        <v>-0.3147</v>
       </c>
       <c r="D78" t="n">
-        <v>-0.5984</v>
+        <v>-0.611</v>
       </c>
       <c r="E78" t="n">
-        <v>-0.4382</v>
+        <v>-0.4194</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.4144</v>
+        <v>-0.4194</v>
       </c>
       <c r="G78" t="n">
-        <v>0.9762</v>
+        <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-1.4144</v>
+        <v>-0.4194</v>
       </c>
       <c r="I78" t="n">
-        <v>-1.4409</v>
+        <v>-0.4194</v>
       </c>
       <c r="J78" t="n">
-        <v>0.9762</v>
+        <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>316</v>
+        <v>211</v>
       </c>
       <c r="L78" t="n">
-        <v>175</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>-0.4647000000000001</v>
+        <v>-0.4194</v>
       </c>
       <c r="N78" t="n">
-        <v>491</v>
+        <v>211</v>
       </c>
     </row>
     <row r="79">
@@ -4038,25 +4038,25 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-0.4692</v>
+        <v>-0.4622</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.3521</v>
+        <v>-0.3468</v>
       </c>
       <c r="D79" t="n">
-        <v>-0.6109</v>
+        <v>-0.6281</v>
       </c>
       <c r="E79" t="n">
-        <v>-0.4692</v>
+        <v>-0.4622</v>
       </c>
       <c r="F79" t="n">
-        <v>-0.4692</v>
+        <v>-0.4622</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>-0.4692</v>
+        <v>-0.4622</v>
       </c>
       <c r="I79" t="n">
         <v>-0.478</v>
@@ -4090,7 +4090,7 @@
         <v>-0.4045</v>
       </c>
       <c r="D80" t="n">
-        <v>-0.6391</v>
+        <v>-0.6586</v>
       </c>
       <c r="E80" t="n">
         <v>-0.539</v>
@@ -4136,7 +4136,7 @@
         <v>-0.4196</v>
       </c>
       <c r="D81" t="n">
-        <v>-0.6473</v>
+        <v>-0.6667</v>
       </c>
       <c r="E81" t="n">
         <v>-0.5592</v>
@@ -4182,7 +4182,7 @@
         <v>-0.4403</v>
       </c>
       <c r="D82" t="n">
-        <v>-0.6584</v>
+        <v>-0.6777</v>
       </c>
       <c r="E82" t="n">
         <v>-0.5868</v>
@@ -4228,7 +4228,7 @@
         <v>-0.449</v>
       </c>
       <c r="D83" t="n">
-        <v>-0.6631</v>
+        <v>-0.6823</v>
       </c>
       <c r="E83" t="n">
         <v>-0.5984</v>
@@ -4268,25 +4268,25 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>-0.6439</v>
+        <v>-0.6415</v>
       </c>
       <c r="C84" t="n">
-        <v>-0.4832</v>
+        <v>-0.4814</v>
       </c>
       <c r="D84" t="n">
-        <v>-0.6815</v>
+        <v>-0.6995</v>
       </c>
       <c r="E84" t="n">
-        <v>-0.6439</v>
+        <v>-0.6415</v>
       </c>
       <c r="F84" t="n">
-        <v>-0.6439</v>
+        <v>-0.6415</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>-0.6439</v>
+        <v>-0.6415</v>
       </c>
       <c r="I84" t="n">
         <v>-0.6469</v>
@@ -4320,7 +4320,7 @@
         <v>-0.4908</v>
       </c>
       <c r="D85" t="n">
-        <v>-0.6856</v>
+        <v>-0.7045</v>
       </c>
       <c r="E85" t="n">
         <v>-0.6541</v>
@@ -4366,7 +4366,7 @@
         <v>-0.4909</v>
       </c>
       <c r="D86" t="n">
-        <v>-0.6856</v>
+        <v>-0.7045</v>
       </c>
       <c r="E86" t="n">
         <v>-0.6542</v>
@@ -4412,7 +4412,7 @@
         <v>-0.4929</v>
       </c>
       <c r="D87" t="n">
-        <v>-0.6867</v>
+        <v>-0.7056</v>
       </c>
       <c r="E87" t="n">
         <v>-0.6569</v>
@@ -4458,7 +4458,7 @@
         <v>-0.5164</v>
       </c>
       <c r="D88" t="n">
-        <v>-0.6994</v>
+        <v>-0.7181</v>
       </c>
       <c r="E88" t="n">
         <v>-0.6882</v>
@@ -4498,25 +4498,25 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>-0.747</v>
+        <v>-0.7415</v>
       </c>
       <c r="C89" t="n">
-        <v>-0.5606</v>
+        <v>-0.5564</v>
       </c>
       <c r="D89" t="n">
-        <v>-0.7231</v>
+        <v>-0.7393</v>
       </c>
       <c r="E89" t="n">
-        <v>-0.747</v>
+        <v>-0.7415</v>
       </c>
       <c r="F89" t="n">
-        <v>-0.747</v>
+        <v>-0.7415</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>-0.747</v>
+        <v>-0.7415</v>
       </c>
       <c r="I89" t="n">
         <v>-0.754</v>
@@ -4544,25 +4544,25 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>-0.802</v>
+        <v>-0.8061</v>
       </c>
       <c r="C90" t="n">
-        <v>-0.6018</v>
+        <v>-0.6049</v>
       </c>
       <c r="D90" t="n">
-        <v>-0.7454</v>
+        <v>-0.7651</v>
       </c>
       <c r="E90" t="n">
-        <v>-0.802</v>
+        <v>-0.8061</v>
       </c>
       <c r="F90" t="n">
-        <v>0.1842</v>
+        <v>0.1801</v>
       </c>
       <c r="G90" t="n">
         <v>-0.9862</v>
       </c>
       <c r="H90" t="n">
-        <v>0.1842</v>
+        <v>0.1801</v>
       </c>
       <c r="I90" t="n">
         <v>0.1894</v>
@@ -4596,7 +4596,7 @@
         <v>-0.6157</v>
       </c>
       <c r="D91" t="n">
-        <v>-0.7528</v>
+        <v>-0.7708</v>
       </c>
       <c r="E91" t="n">
         <v>-0.8205</v>
@@ -4642,7 +4642,7 @@
         <v>-0.6484</v>
       </c>
       <c r="D92" t="n">
-        <v>-0.7704</v>
+        <v>-0.7882</v>
       </c>
       <c r="E92" t="n">
         <v>-0.8641</v>
@@ -4688,7 +4688,7 @@
         <v>-0.7504</v>
       </c>
       <c r="D93" t="n">
-        <v>-0.8253</v>
+        <v>-0.8423</v>
       </c>
       <c r="E93" t="n">
         <v>-1</v>
@@ -4734,7 +4734,7 @@
         <v>-0.7825</v>
       </c>
       <c r="D94" t="n">
-        <v>-0.8426</v>
+        <v>-0.8593</v>
       </c>
       <c r="E94" t="n">
         <v>-1.0427</v>
@@ -4774,25 +4774,25 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>-1.0907</v>
+        <v>-1.0867</v>
       </c>
       <c r="C95" t="n">
-        <v>-0.8185</v>
+        <v>-0.8155</v>
       </c>
       <c r="D95" t="n">
-        <v>-0.862</v>
+        <v>-0.8769</v>
       </c>
       <c r="E95" t="n">
-        <v>-1.0907</v>
+        <v>-1.0867</v>
       </c>
       <c r="F95" t="n">
-        <v>-1.0907</v>
+        <v>-1.0867</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>-1.0907</v>
+        <v>-1.0867</v>
       </c>
       <c r="I95" t="n">
         <v>-1.0958</v>
@@ -4826,7 +4826,7 @@
         <v>-0.8339</v>
       </c>
       <c r="D96" t="n">
-        <v>-0.8703</v>
+        <v>-0.8867</v>
       </c>
       <c r="E96" t="n">
         <v>-1.1113</v>
@@ -4872,7 +4872,7 @@
         <v>-0.8563</v>
       </c>
       <c r="D97" t="n">
-        <v>-0.8823</v>
+        <v>-0.8985</v>
       </c>
       <c r="E97" t="n">
         <v>-1.1411</v>
@@ -4908,93 +4908,93 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ANDROID</t>
+          <t>hazed</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>-1.3903</v>
+        <v>-1.386</v>
       </c>
       <c r="C98" t="n">
-        <v>-1.0433</v>
+        <v>-1.0401</v>
       </c>
       <c r="D98" t="n">
-        <v>-0.983</v>
+        <v>-0.9961</v>
       </c>
       <c r="E98" t="n">
-        <v>-1.3903</v>
+        <v>-1.386</v>
       </c>
       <c r="F98" t="n">
-        <v>-1.3903</v>
+        <v>-1.386</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>-1.3903</v>
+        <v>-1.386</v>
       </c>
       <c r="I98" t="n">
-        <v>-1.3903</v>
+        <v>-1.4333</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>211</v>
+        <v>396</v>
       </c>
       <c r="L98" t="n">
         <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>-1.3903</v>
+        <v>-1.4333</v>
       </c>
       <c r="N98" t="n">
-        <v>211</v>
+        <v>396</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>hazed</t>
+          <t>ANDROID</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>-1.4069</v>
+        <v>-1.3903</v>
       </c>
       <c r="C99" t="n">
-        <v>-1.0558</v>
+        <v>-1.0433</v>
       </c>
       <c r="D99" t="n">
-        <v>-0.9897</v>
+        <v>-0.9978</v>
       </c>
       <c r="E99" t="n">
-        <v>-1.4069</v>
+        <v>-1.3903</v>
       </c>
       <c r="F99" t="n">
-        <v>-1.4069</v>
+        <v>-1.3903</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>-1.4069</v>
+        <v>-1.3903</v>
       </c>
       <c r="I99" t="n">
-        <v>-1.4333</v>
+        <v>-1.3903</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>396</v>
+        <v>211</v>
       </c>
       <c r="L99" t="n">
         <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>-1.4333</v>
+        <v>-1.3903</v>
       </c>
       <c r="N99" t="n">
-        <v>396</v>
+        <v>211</v>
       </c>
     </row>
     <row r="100">
@@ -5004,25 +5004,25 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>-1.4465</v>
+        <v>-1.4411</v>
       </c>
       <c r="C100" t="n">
-        <v>-1.0855</v>
+        <v>-1.0814</v>
       </c>
       <c r="D100" t="n">
-        <v>-1.0057</v>
+        <v>-1.018</v>
       </c>
       <c r="E100" t="n">
-        <v>-1.4465</v>
+        <v>-1.4411</v>
       </c>
       <c r="F100" t="n">
-        <v>-1.4465</v>
+        <v>-1.4411</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
       </c>
       <c r="H100" t="n">
-        <v>-1.4465</v>
+        <v>-1.4411</v>
       </c>
       <c r="I100" t="n">
         <v>-1.4532</v>
@@ -5056,7 +5056,7 @@
         <v>-1.1187</v>
       </c>
       <c r="D101" t="n">
-        <v>-1.0236</v>
+        <v>-1.0378</v>
       </c>
       <c r="E101" t="n">
         <v>-1.4908</v>
@@ -5102,7 +5102,7 @@
         <v>-1.1323</v>
       </c>
       <c r="D102" t="n">
-        <v>-1.0309</v>
+        <v>-1.0451</v>
       </c>
       <c r="E102" t="n">
         <v>-1.5089</v>
@@ -5142,25 +5142,25 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>-1.5301</v>
+        <v>-1.5338</v>
       </c>
       <c r="C103" t="n">
-        <v>-1.1482</v>
+        <v>-1.151</v>
       </c>
       <c r="D103" t="n">
-        <v>-1.0395</v>
+        <v>-1.055</v>
       </c>
       <c r="E103" t="n">
-        <v>-1.5301</v>
+        <v>-1.5338</v>
       </c>
       <c r="F103" t="n">
-        <v>0.3323</v>
+        <v>0.3286</v>
       </c>
       <c r="G103" t="n">
         <v>-1.8624</v>
       </c>
       <c r="H103" t="n">
-        <v>0.3323</v>
+        <v>0.3286</v>
       </c>
       <c r="I103" t="n">
         <v>0.337</v>
@@ -5188,25 +5188,25 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>-1.5837</v>
+        <v>-1.566</v>
       </c>
       <c r="C104" t="n">
-        <v>-1.1884</v>
+        <v>-1.1751</v>
       </c>
       <c r="D104" t="n">
-        <v>-1.0611</v>
+        <v>-1.0678</v>
       </c>
       <c r="E104" t="n">
-        <v>-1.5837</v>
+        <v>-1.566</v>
       </c>
       <c r="F104" t="n">
-        <v>-1.5837</v>
+        <v>-1.566</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
       </c>
       <c r="H104" t="n">
-        <v>-1.5837</v>
+        <v>-1.566</v>
       </c>
       <c r="I104" t="n">
         <v>-1.6059</v>
@@ -5240,7 +5240,7 @@
         <v>-1.2201</v>
       </c>
       <c r="D105" t="n">
-        <v>-1.0782</v>
+        <v>-1.0917</v>
       </c>
       <c r="E105" t="n">
         <v>-1.6259</v>
@@ -5280,25 +5280,25 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>-1.6757</v>
+        <v>-1.6308</v>
       </c>
       <c r="C106" t="n">
-        <v>-1.2575</v>
+        <v>-1.2238</v>
       </c>
       <c r="D106" t="n">
-        <v>-1.0983</v>
+        <v>-1.0936</v>
       </c>
       <c r="E106" t="n">
-        <v>-1.6757</v>
+        <v>-1.6308</v>
       </c>
       <c r="F106" t="n">
-        <v>-2.0271</v>
+        <v>-1.9822</v>
       </c>
       <c r="G106" t="n">
         <v>0.3514</v>
       </c>
       <c r="H106" t="n">
-        <v>-2.0271</v>
+        <v>-1.9822</v>
       </c>
       <c r="I106" t="n">
         <v>-2.0844</v>
@@ -5332,7 +5332,7 @@
         <v>-1.2584</v>
       </c>
       <c r="D107" t="n">
-        <v>-1.0988</v>
+        <v>-1.112</v>
       </c>
       <c r="E107" t="n">
         <v>-1.677</v>
@@ -5368,93 +5368,93 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>mitch</t>
+          <t>B1ad3</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>-1.8069</v>
+        <v>-1.7995</v>
       </c>
       <c r="C108" t="n">
-        <v>-1.3559</v>
+        <v>-1.3504</v>
       </c>
       <c r="D108" t="n">
-        <v>-1.1513</v>
+        <v>-1.1608</v>
       </c>
       <c r="E108" t="n">
-        <v>-1.8069</v>
+        <v>-1.7995</v>
       </c>
       <c r="F108" t="n">
-        <v>-1.8069</v>
+        <v>-1.7995</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
       </c>
       <c r="H108" t="n">
-        <v>-1.8069</v>
+        <v>-1.7995</v>
       </c>
       <c r="I108" t="n">
-        <v>-1.8069</v>
+        <v>-1.8299</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
       </c>
       <c r="K108" t="n">
-        <v>198</v>
+        <v>281</v>
       </c>
       <c r="L108" t="n">
         <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>-1.8069</v>
+        <v>-1.8299</v>
       </c>
       <c r="N108" t="n">
-        <v>198</v>
+        <v>281</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>B1ad3</t>
+          <t>mitch</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>-1.813</v>
+        <v>-1.8069</v>
       </c>
       <c r="C109" t="n">
-        <v>-1.3605</v>
+        <v>-1.3559</v>
       </c>
       <c r="D109" t="n">
-        <v>-1.1538</v>
+        <v>-1.1638</v>
       </c>
       <c r="E109" t="n">
-        <v>-1.813</v>
+        <v>-1.8069</v>
       </c>
       <c r="F109" t="n">
-        <v>-1.813</v>
+        <v>-1.8069</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
       </c>
       <c r="H109" t="n">
-        <v>-1.813</v>
+        <v>-1.8069</v>
       </c>
       <c r="I109" t="n">
-        <v>-1.8299</v>
+        <v>-1.8069</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
       </c>
       <c r="K109" t="n">
-        <v>281</v>
+        <v>198</v>
       </c>
       <c r="L109" t="n">
         <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>-1.8299</v>
+        <v>-1.8069</v>
       </c>
       <c r="N109" t="n">
-        <v>281</v>
+        <v>198</v>
       </c>
     </row>
     <row r="110">
@@ -5464,25 +5464,25 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>-1.9727</v>
+        <v>-1.9603</v>
       </c>
       <c r="C110" t="n">
-        <v>-1.4803</v>
+        <v>-1.471</v>
       </c>
       <c r="D110" t="n">
-        <v>-1.2183</v>
+        <v>-1.2249</v>
       </c>
       <c r="E110" t="n">
-        <v>-1.9727</v>
+        <v>-1.9603</v>
       </c>
       <c r="F110" t="n">
-        <v>-1.1128</v>
+        <v>-1.1004</v>
       </c>
       <c r="G110" t="n">
         <v>-0.8599</v>
       </c>
       <c r="H110" t="n">
-        <v>-1.1128</v>
+        <v>-1.1004</v>
       </c>
       <c r="I110" t="n">
         <v>-1.1284</v>
@@ -5510,25 +5510,25 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>-2.0391</v>
+        <v>-2.0315</v>
       </c>
       <c r="C111" t="n">
-        <v>-1.5302</v>
+        <v>-1.5245</v>
       </c>
       <c r="D111" t="n">
-        <v>-1.2451</v>
+        <v>-1.2533</v>
       </c>
       <c r="E111" t="n">
-        <v>-2.0391</v>
+        <v>-2.0315</v>
       </c>
       <c r="F111" t="n">
-        <v>-2.0391</v>
+        <v>-2.0315</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
       </c>
       <c r="H111" t="n">
-        <v>-2.0391</v>
+        <v>-2.0315</v>
       </c>
       <c r="I111" t="n">
         <v>-2.0486</v>
@@ -5562,7 +5562,7 @@
         <v>-1.5472</v>
       </c>
       <c r="D112" t="n">
-        <v>-1.2543</v>
+        <v>-1.2653</v>
       </c>
       <c r="E112" t="n">
         <v>-2.0618</v>
@@ -5608,7 +5608,7 @@
         <v>-1.5535</v>
       </c>
       <c r="D113" t="n">
-        <v>-1.2577</v>
+        <v>-1.2687</v>
       </c>
       <c r="E113" t="n">
         <v>-2.0702</v>
@@ -5654,7 +5654,7 @@
         <v>-1.5537</v>
       </c>
       <c r="D114" t="n">
-        <v>-1.2578</v>
+        <v>-1.2688</v>
       </c>
       <c r="E114" t="n">
         <v>-2.0704</v>
@@ -5700,7 +5700,7 @@
         <v>-1.633</v>
       </c>
       <c r="D115" t="n">
-        <v>-1.3005</v>
+        <v>-1.3109</v>
       </c>
       <c r="E115" t="n">
         <v>-2.1762</v>
@@ -5736,139 +5736,139 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>adreN</t>
+          <t>reltuC</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>-2.2729</v>
+        <v>-2.2578</v>
       </c>
       <c r="C116" t="n">
-        <v>-1.7056</v>
+        <v>-1.6943</v>
       </c>
       <c r="D116" t="n">
-        <v>-1.3396</v>
+        <v>-1.3434</v>
       </c>
       <c r="E116" t="n">
-        <v>-2.2729</v>
+        <v>-2.2578</v>
       </c>
       <c r="F116" t="n">
-        <v>-2.2729</v>
+        <v>-2.2578</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
       </c>
       <c r="H116" t="n">
-        <v>-2.2729</v>
+        <v>-2.2578</v>
       </c>
       <c r="I116" t="n">
-        <v>-2.2729</v>
+        <v>-2.3348</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
       </c>
       <c r="K116" t="n">
-        <v>203</v>
+        <v>396</v>
       </c>
       <c r="L116" t="n">
         <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>-2.2729</v>
+        <v>-2.3348</v>
       </c>
       <c r="N116" t="n">
-        <v>203</v>
+        <v>396</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>dephh</t>
+          <t>adreN</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>-2.2848</v>
+        <v>-2.2729</v>
       </c>
       <c r="C117" t="n">
-        <v>-1.7145</v>
+        <v>-1.7056</v>
       </c>
       <c r="D117" t="n">
-        <v>-1.3444</v>
+        <v>-1.3494</v>
       </c>
       <c r="E117" t="n">
-        <v>-2.2848</v>
+        <v>-2.2729</v>
       </c>
       <c r="F117" t="n">
-        <v>-2.2848</v>
+        <v>-2.2729</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
       </c>
       <c r="H117" t="n">
-        <v>-2.2848</v>
+        <v>-2.2729</v>
       </c>
       <c r="I117" t="n">
-        <v>-2.2848</v>
+        <v>-2.2729</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
       </c>
       <c r="K117" t="n">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="L117" t="n">
         <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>-2.2848</v>
+        <v>-2.2729</v>
       </c>
       <c r="N117" t="n">
-        <v>211</v>
+        <v>203</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>reltuC</t>
+          <t>dephh</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>-2.2918</v>
+        <v>-2.2848</v>
       </c>
       <c r="C118" t="n">
-        <v>-1.7198</v>
+        <v>-1.7145</v>
       </c>
       <c r="D118" t="n">
-        <v>-1.3472</v>
+        <v>-1.3542</v>
       </c>
       <c r="E118" t="n">
-        <v>-2.2918</v>
+        <v>-2.2848</v>
       </c>
       <c r="F118" t="n">
-        <v>-2.2918</v>
+        <v>-2.2848</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
       </c>
       <c r="H118" t="n">
-        <v>-2.2918</v>
+        <v>-2.2848</v>
       </c>
       <c r="I118" t="n">
-        <v>-2.3348</v>
+        <v>-2.2848</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
       </c>
       <c r="K118" t="n">
-        <v>396</v>
+        <v>211</v>
       </c>
       <c r="L118" t="n">
         <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>-2.3348</v>
+        <v>-2.2848</v>
       </c>
       <c r="N118" t="n">
-        <v>396</v>
+        <v>211</v>
       </c>
     </row>
     <row r="119">
@@ -5884,7 +5884,7 @@
         <v>-1.7632</v>
       </c>
       <c r="D119" t="n">
-        <v>-1.3705</v>
+        <v>-1.38</v>
       </c>
       <c r="E119" t="n">
         <v>-2.3496</v>
@@ -5924,25 +5924,25 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>-2.7812</v>
+        <v>-2.7708</v>
       </c>
       <c r="C120" t="n">
-        <v>-2.087</v>
+        <v>-2.0792</v>
       </c>
       <c r="D120" t="n">
-        <v>-1.5449</v>
+        <v>-1.5478</v>
       </c>
       <c r="E120" t="n">
-        <v>-2.7812</v>
+        <v>-2.7708</v>
       </c>
       <c r="F120" t="n">
-        <v>-2.7812</v>
+        <v>-2.7708</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
       </c>
       <c r="H120" t="n">
-        <v>-2.7812</v>
+        <v>-2.7708</v>
       </c>
       <c r="I120" t="n">
         <v>-2.7941</v>
@@ -5976,7 +5976,7 @@
         <v>-2.3568</v>
       </c>
       <c r="D121" t="n">
-        <v>-1.6901</v>
+        <v>-1.6952</v>
       </c>
       <c r="E121" t="n">
         <v>-3.1407</v>
@@ -6022,7 +6022,7 @@
         <v>-2.3865</v>
       </c>
       <c r="D122" t="n">
-        <v>-1.7061</v>
+        <v>-1.7109</v>
       </c>
       <c r="E122" t="n">
         <v>-3.1803</v>
@@ -6062,25 +6062,25 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>-3.2078</v>
+        <v>-3.1839</v>
       </c>
       <c r="C123" t="n">
-        <v>-2.4072</v>
+        <v>-2.3892</v>
       </c>
       <c r="D123" t="n">
-        <v>-1.7172</v>
+        <v>-1.7124</v>
       </c>
       <c r="E123" t="n">
-        <v>-3.2078</v>
+        <v>-3.1839</v>
       </c>
       <c r="F123" t="n">
-        <v>-3.2078</v>
+        <v>-3.1839</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
       </c>
       <c r="H123" t="n">
-        <v>-3.2078</v>
+        <v>-3.1839</v>
       </c>
       <c r="I123" t="n">
         <v>-3.2377</v>
@@ -6114,7 +6114,7 @@
         <v>-2.7082</v>
       </c>
       <c r="D124" t="n">
-        <v>-1.8793</v>
+        <v>-1.8817</v>
       </c>
       <c r="E124" t="n">
         <v>-3.6089</v>
@@ -6154,25 +6154,25 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>-4.6518</v>
+        <v>-4.5828</v>
       </c>
       <c r="C125" t="n">
-        <v>-3.4908</v>
+        <v>-3.439</v>
       </c>
       <c r="D125" t="n">
-        <v>-2.3006</v>
+        <v>-2.2697</v>
       </c>
       <c r="E125" t="n">
-        <v>-4.6518</v>
+        <v>-4.5828</v>
       </c>
       <c r="F125" t="n">
-        <v>-4.6518</v>
+        <v>-4.5828</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
       </c>
       <c r="H125" t="n">
-        <v>-4.6518</v>
+        <v>-4.5828</v>
       </c>
       <c r="I125" t="n">
         <v>-4.739</v>
